--- a/data/trans_dic/P64D$publico_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P64D$publico_2023-Clase-trans_dic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 10,13</t>
+          <t>4,46; 10,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 12,93</t>
+          <t>7,16; 13,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,43</t>
+          <t>6,3; 10,15</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 11,36</t>
+          <t>5,15; 11,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 13,99</t>
+          <t>7,11; 13,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,43</t>
+          <t>6,7; 11,19</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,17</t>
+          <t>0,56; 7,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,17</t>
+          <t>0,81; 7,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,35</t>
+          <t>0,81; 6,33</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 10,17</t>
+          <t>5,26; 10,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,26; 14,38</t>
+          <t>8,24; 14,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,12</t>
+          <t>7,22; 11,16</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 12,6</t>
+          <t>5,25; 12,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,32; 17,12</t>
+          <t>5,92; 17,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,84; 13,94</t>
+          <t>6,74; 13,74</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -822,84 +822,33 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,33; 7,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,39; 11,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,09; 9,23</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10,22%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>4,26; 7,91</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>8,37; 11,99</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>6,12; 9,31</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>
@@ -914,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -927,7 +876,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14320; 35531</t>
+          <t>15633; 36128</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22684; 40415</t>
+          <t>22367; 40664</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41829; 69180</t>
+          <t>41809; 67307</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15406; 34472</t>
+          <t>15625; 33981</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18178; 35273</t>
+          <t>17917; 34805</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38130; 63469</t>
+          <t>37232; 62129</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3281; 35096</t>
+          <t>2748; 35342</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>586; 5253</t>
+          <t>595; 5636</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3562; 35727</t>
+          <t>4544; 35628</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29830; 56931</t>
+          <t>29419; 57593</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35210; 61341</t>
+          <t>35123; 60549</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71529; 109613</t>
+          <t>71190; 110023</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1273,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13075; 30226</t>
+          <t>12589; 31050</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23619; 63926</t>
+          <t>22102; 64921</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41969; 85492</t>
+          <t>41341; 84273</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1351,17 +1300,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>205</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>333</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>124055</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>147015</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271070</t>
         </is>
       </c>
     </row>
@@ -1397,109 +1346,35 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84054; 154579</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>120606; 172420</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>205855; 312178</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>124055</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>147015</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>271070</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>82818; 153698</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>120307; 172459</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>207077; 314902</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P64D$publico_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P64D$publico_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 10,3</t>
+          <t>4,69; 10,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 13,01</t>
+          <t>7,53; 13,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 10,15</t>
+          <t>6,52; 10,59</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,2</t>
+          <t>5,33; 11,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 13,8</t>
+          <t>7,25; 14,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 11,19</t>
+          <t>7,19; 11,76</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 7,22</t>
+          <t>3,8; 11,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,7</t>
+          <t>0,0; 6,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,33</t>
+          <t>3,51; 9,77</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 10,29</t>
+          <t>6,27; 11,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,24; 14,2</t>
+          <t>8,82; 14,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 11,16</t>
+          <t>8,3; 11,94</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 12,94</t>
+          <t>6,61; 13,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,92; 17,38</t>
+          <t>12,63; 19,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,74; 13,74</t>
+          <t>10,33; 15,87</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,95</t>
+          <t>6,82; 9,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,39; 11,99</t>
+          <t>9,9; 12,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,09; 9,23</t>
+          <t>8,63; 10,67</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>26715</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30421</t>
+          <t>33247</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54180</t>
+          <t>59962</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15633; 36128</t>
+          <t>17892; 41089</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22367; 40664</t>
+          <t>25080; 44294</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41809; 67307</t>
+          <t>46612; 75659</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>23515</t>
+          <t>26637</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25779</t>
+          <t>28017</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49294</t>
+          <t>54654</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15625; 33981</t>
+          <t>17116; 38208</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17917; 34805</t>
+          <t>19822; 39509</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37232; 62129</t>
+          <t>42759; 69872</t>
         </is>
       </c>
     </row>
@@ -1104,17 +1104,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14585</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>20680</t>
         </is>
       </c>
     </row>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2748; 35342</t>
+          <t>10308; 30033</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>595; 5636</t>
+          <t>0; 5612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4544; 35628</t>
+          <t>12434; 34610</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>42078</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>46411</t>
+          <t>55985</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88489</t>
+          <t>109359</t>
         </is>
       </c>
     </row>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29419; 57593</t>
+          <t>38893; 72809</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35123; 60549</t>
+          <t>42231; 71454</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71190; 110023</t>
+          <t>91259; 131229</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>28861</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42523</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62641</t>
+          <t>79268</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12589; 31050</t>
+          <t>20297; 42132</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22102; 64921</t>
+          <t>39521; 61968</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41341; 84273</t>
+          <t>64044; 98371</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>124055</t>
+          <t>154184</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>147015</t>
+          <t>169739</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271070</t>
+          <t>323924</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>84054; 154579</t>
+          <t>129663; 178863</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>120606; 172420</t>
+          <t>146704; 191700</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>205855; 312178</t>
+          <t>291768; 361033</t>
         </is>
       </c>
     </row>
